--- a/public/CuentasCuentas/7000-Recaudado-Renovacion-CuentasCuentasSeguidas.xlsx
+++ b/public/CuentasCuentas/7000-Recaudado-Renovacion-CuentasCuentasSeguidas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SAC-IPE\public\CuentasCuentas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\CuentasCuentas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046D74C0-28B1-4012-B3D1-6A2BAAE27CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEDC594-4842-4953-A607-1F3C3CCDCC9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="21">
   <si>
     <t>cuenta</t>
   </si>
@@ -97,6 +97,9 @@
   <si>
     <t xml:space="preserve">Por el recaudo de Ingresos por Venta de Bienes, Prestación de Servicios de Instituciones Públicas de Seguridad Social. (Préstamos con Renovación)
 </t>
+  </si>
+  <si>
+    <t>1.1.1.1.01.01</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="78.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -951,14 +954,32 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+      <c r="A34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
+      <c r="A35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
